--- a/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9720_colegio-hernan-olguin_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8C62F31-6703-44B3-82A8-669A15CA5C9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6D9A376-9E2B-449E-922F-CC21F135BB0C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{247CDE7F-C379-407C-B2AF-756D8361CC97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A711DC7-2DB1-4C98-B75D-B5FC44D0A6D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45605B64-E5DE-41F1-94BB-9960D1B4DD26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67FACCB7-B24C-47E2-BC13-3B03CE6E9229}"/>
 </file>